--- a/Modules/S&S/S&S_BOM.xlsx
+++ b/Modules/S&S/S&S_BOM.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29426"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29929"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\My-Dev\Modular Synth\Avalon Harmonics\S&amp;S\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A2E185BA-7DF5-4D03-82C9-EB50A0C79444}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FDF5A1C1-69B9-493B-8E3E-DAF267D12B3F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="BOM" sheetId="1" r:id="rId1"/>
@@ -239,15 +239,9 @@
     <t>Pushernut</t>
   </si>
   <si>
-    <t>https://pushermanproductions.com/product/black-smooth-edge-jack-nuts-pack-of-25/</t>
-  </si>
-  <si>
     <t>Gold</t>
   </si>
   <si>
-    <t>https://pushermanproductions.com/product/pushernuts-gold-smooth-edge-jack-nuts-pack-of-25/</t>
-  </si>
-  <si>
     <t>Potentiometer Nut</t>
   </si>
   <si>
@@ -710,9 +704,6 @@
     <t>https://www.tme.eu/de/en/details/zl201-40g/pin-headers/connfly/ds1021-1-40sf11-b/</t>
   </si>
   <si>
-    <t>https://www.tme.eu/de/en/details/zl202-80g/pin-headers/connfly/ds1021-2-40sf11/</t>
-  </si>
-  <si>
     <t>https://www.tme.eu/de/en/details/mks2-10u_50v/tht-film-capacitors/wima/mks2b051001n00kssd/</t>
   </si>
   <si>
@@ -957,6 +948,15 @@
   </si>
   <si>
     <t>LED 3mm Dome Bicolor</t>
+  </si>
+  <si>
+    <t>https://pushermanproductions.com/products/pushernuts-round-mini-jack-nuts-pack-of-25?variant=57164621578504</t>
+  </si>
+  <si>
+    <t>https://pushermanproductions.com/products/pushernuts-round-mini-jack-nuts-pack-of-25?variant=57166910816520</t>
+  </si>
+  <si>
+    <t>https://www.tme.eu/de/en/details/zl202-10g/pin-headers/connfly/ds1021-2-5sf11-b/</t>
   </si>
 </sst>
 </file>
@@ -1889,7 +1889,7 @@
   <sheetData>
     <row r="1" spans="1:10" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" s="8" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
     </row>
     <row r="2" spans="1:10" x14ac:dyDescent="0.25">
@@ -1913,7 +1913,7 @@
       </c>
       <c r="G2" s="3"/>
       <c r="J2" s="3" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
     </row>
     <row r="3" spans="1:10" x14ac:dyDescent="0.25">
@@ -1924,7 +1924,7 @@
         <v>330</v>
       </c>
       <c r="C3" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="D3" s="9" t="s">
         <v>26</v>
@@ -1933,7 +1933,7 @@
         <v>34</v>
       </c>
       <c r="F3" s="5" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="J3" s="5" t="s">
         <v>55</v>
@@ -1947,16 +1947,16 @@
         <v>27</v>
       </c>
       <c r="C4" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="D4" t="s">
-        <v>166</v>
+        <v>163</v>
       </c>
       <c r="E4" t="s">
         <v>34</v>
       </c>
       <c r="F4" s="5" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="J4" s="5" t="s">
         <v>55</v>
@@ -1970,7 +1970,7 @@
         <v>23</v>
       </c>
       <c r="C5" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="D5" t="s">
         <v>24</v>
@@ -1979,7 +1979,7 @@
         <v>34</v>
       </c>
       <c r="F5" s="5" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="J5" s="5" t="s">
         <v>55</v>
@@ -1993,7 +1993,7 @@
         <v>28</v>
       </c>
       <c r="C6" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="D6" t="s">
         <v>29</v>
@@ -2002,10 +2002,10 @@
         <v>34</v>
       </c>
       <c r="F6" s="5" t="s">
-        <v>139</v>
+        <v>137</v>
       </c>
       <c r="J6" s="5" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
     </row>
     <row r="7" spans="1:10" x14ac:dyDescent="0.25">
@@ -2013,22 +2013,22 @@
         <v>1</v>
       </c>
       <c r="B7" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="C7" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="D7" s="7" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="E7" t="s">
         <v>34</v>
       </c>
       <c r="F7" s="5" t="s">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="J7" s="5" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
     </row>
     <row r="8" spans="1:10" x14ac:dyDescent="0.25">
@@ -2039,16 +2039,16 @@
         <v>30</v>
       </c>
       <c r="C8" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="D8" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="E8" t="s">
         <v>34</v>
       </c>
       <c r="F8" s="5" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="J8" s="5" t="s">
         <v>55</v>
@@ -2062,16 +2062,16 @@
         <v>25</v>
       </c>
       <c r="C9" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="D9" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="E9" t="s">
         <v>34</v>
       </c>
       <c r="F9" s="5" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="J9" s="5" t="s">
         <v>55</v>
@@ -2085,16 +2085,16 @@
         <v>21</v>
       </c>
       <c r="C10" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="D10" t="s">
-        <v>167</v>
+        <v>164</v>
       </c>
       <c r="E10" t="s">
         <v>34</v>
       </c>
       <c r="F10" s="5" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="J10" s="5" t="s">
         <v>55</v>
@@ -2108,7 +2108,7 @@
         <v>52</v>
       </c>
       <c r="C11" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="D11" t="s">
         <v>53</v>
@@ -2120,7 +2120,7 @@
         <v>55</v>
       </c>
       <c r="J11" s="5" t="s">
-        <v>164</v>
+        <v>161</v>
       </c>
     </row>
     <row r="12" spans="1:10" x14ac:dyDescent="0.25">
@@ -2131,16 +2131,16 @@
         <v>22</v>
       </c>
       <c r="C12" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="D12" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="E12" t="s">
         <v>34</v>
       </c>
       <c r="F12" s="5" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
       <c r="J12" s="5" t="s">
         <v>55</v>
@@ -2154,19 +2154,19 @@
         <v>8</v>
       </c>
       <c r="C13" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="D13" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="E13" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="F13" s="5" t="s">
-        <v>145</v>
+        <v>143</v>
       </c>
       <c r="J13" t="s">
-        <v>160</v>
+        <v>157</v>
       </c>
     </row>
     <row r="14" spans="1:10" x14ac:dyDescent="0.25">
@@ -2177,19 +2177,19 @@
         <v>7</v>
       </c>
       <c r="C14" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="D14" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="E14" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="F14" s="5" t="s">
-        <v>146</v>
+        <v>144</v>
       </c>
       <c r="J14" t="s">
-        <v>160</v>
+        <v>157</v>
       </c>
     </row>
     <row r="15" spans="1:10" x14ac:dyDescent="0.25">
@@ -2200,19 +2200,19 @@
         <v>9</v>
       </c>
       <c r="C15" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="D15" s="7" t="s">
         <v>10</v>
       </c>
       <c r="E15" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="F15" s="5" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="J15" t="s">
-        <v>160</v>
+        <v>157</v>
       </c>
     </row>
     <row r="16" spans="1:10" x14ac:dyDescent="0.25">
@@ -2220,22 +2220,22 @@
         <v>1</v>
       </c>
       <c r="B16" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="D16" s="7" t="s">
         <v>11</v>
       </c>
       <c r="E16" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="F16" s="5" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
       <c r="J16" s="5" t="s">
-        <v>159</v>
+        <v>156</v>
       </c>
     </row>
     <row r="17" spans="1:10" x14ac:dyDescent="0.25">
@@ -2246,19 +2246,19 @@
         <v>5</v>
       </c>
       <c r="C17" t="s">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="D17" s="7" t="s">
         <v>6</v>
       </c>
       <c r="E17" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="F17" s="5" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
       <c r="J17" t="s">
-        <v>160</v>
+        <v>157</v>
       </c>
     </row>
     <row r="18" spans="1:10" x14ac:dyDescent="0.25">
@@ -2278,10 +2278,10 @@
         <v>37</v>
       </c>
       <c r="F18" s="5" t="s">
-        <v>150</v>
+        <v>148</v>
       </c>
       <c r="J18" t="s">
-        <v>160</v>
+        <v>157</v>
       </c>
     </row>
     <row r="19" spans="1:10" x14ac:dyDescent="0.25">
@@ -2295,16 +2295,16 @@
         <v>36</v>
       </c>
       <c r="D19" s="7" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="E19" t="s">
         <v>38</v>
       </c>
       <c r="F19" s="5" t="s">
-        <v>151</v>
+        <v>149</v>
       </c>
       <c r="J19" t="s">
-        <v>160</v>
+        <v>157</v>
       </c>
     </row>
     <row r="20" spans="1:10" x14ac:dyDescent="0.25">
@@ -2312,22 +2312,22 @@
         <v>1</v>
       </c>
       <c r="B20" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="C20" t="s">
         <v>36</v>
       </c>
       <c r="D20" s="7" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="E20" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="F20" s="5" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="J20" t="s">
-        <v>160</v>
+        <v>157</v>
       </c>
     </row>
     <row r="21" spans="1:10" x14ac:dyDescent="0.25">
@@ -2347,10 +2347,10 @@
         <v>45</v>
       </c>
       <c r="F21" s="5" t="s">
-        <v>153</v>
+        <v>151</v>
       </c>
       <c r="J21" t="s">
-        <v>160</v>
+        <v>157</v>
       </c>
     </row>
     <row r="22" spans="1:10" x14ac:dyDescent="0.25">
@@ -2358,7 +2358,7 @@
         <v>1</v>
       </c>
       <c r="B22" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="C22" t="s">
         <v>44</v>
@@ -2367,13 +2367,13 @@
         <v>20</v>
       </c>
       <c r="E22" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="F22" s="5" t="s">
-        <v>154</v>
+        <v>152</v>
       </c>
       <c r="J22" t="s">
-        <v>160</v>
+        <v>157</v>
       </c>
     </row>
     <row r="23" spans="1:10" x14ac:dyDescent="0.25">
@@ -2387,16 +2387,16 @@
         <v>48</v>
       </c>
       <c r="D23" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="E23" t="s">
         <v>49</v>
       </c>
       <c r="F23" s="5" t="s">
-        <v>161</v>
+        <v>158</v>
       </c>
       <c r="J23" s="5" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
     </row>
     <row r="24" spans="1:10" x14ac:dyDescent="0.25">
@@ -2404,22 +2404,22 @@
         <v>1</v>
       </c>
       <c r="B24" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="C24" t="s">
         <v>47</v>
       </c>
       <c r="D24" s="7" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="E24" t="s">
         <v>50</v>
       </c>
       <c r="F24" s="5" t="s">
-        <v>155</v>
+        <v>153</v>
       </c>
       <c r="J24" t="s">
-        <v>160</v>
+        <v>157</v>
       </c>
     </row>
     <row r="25" spans="1:10" x14ac:dyDescent="0.25">
@@ -2433,16 +2433,16 @@
         <v>47</v>
       </c>
       <c r="D25" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="E25" t="s">
         <v>50</v>
       </c>
       <c r="F25" s="5" t="s">
-        <v>155</v>
+        <v>153</v>
       </c>
       <c r="J25" t="s">
-        <v>160</v>
+        <v>157</v>
       </c>
     </row>
     <row r="26" spans="1:10" x14ac:dyDescent="0.25">
@@ -2453,19 +2453,19 @@
         <v>17</v>
       </c>
       <c r="C26" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="D26" s="9" t="s">
         <v>42</v>
       </c>
       <c r="E26" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="F26" s="5" t="s">
         <v>56</v>
       </c>
       <c r="J26" t="s">
-        <v>160</v>
+        <v>157</v>
       </c>
     </row>
     <row r="27" spans="1:10" x14ac:dyDescent="0.25">
@@ -2476,7 +2476,7 @@
         <v>40</v>
       </c>
       <c r="C27" t="s">
-        <v>171</v>
+        <v>168</v>
       </c>
       <c r="D27" s="9" t="s">
         <v>43</v>
@@ -2485,10 +2485,10 @@
         <v>41</v>
       </c>
       <c r="F27" s="5" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="J27" t="s">
-        <v>160</v>
+        <v>157</v>
       </c>
     </row>
     <row r="28" spans="1:10" x14ac:dyDescent="0.25">
@@ -2499,10 +2499,10 @@
         <v>51</v>
       </c>
       <c r="C28" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="D28" t="s">
-        <v>168</v>
+        <v>165</v>
       </c>
       <c r="E28" t="s">
         <v>46</v>
@@ -2511,7 +2511,7 @@
         <v>57</v>
       </c>
       <c r="J28" t="s">
-        <v>160</v>
+        <v>157</v>
       </c>
     </row>
     <row r="29" spans="1:10" x14ac:dyDescent="0.25">
@@ -2519,13 +2519,13 @@
         <v>4</v>
       </c>
       <c r="B29" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="C29" t="s">
         <v>58</v>
       </c>
       <c r="D29" t="s">
-        <v>169</v>
+        <v>166</v>
       </c>
       <c r="E29" t="s">
         <v>39</v>
@@ -2534,7 +2534,7 @@
         <v>59</v>
       </c>
       <c r="J29" t="s">
-        <v>160</v>
+        <v>157</v>
       </c>
     </row>
     <row r="30" spans="1:10" x14ac:dyDescent="0.25">
@@ -2542,22 +2542,22 @@
         <v>4</v>
       </c>
       <c r="B30" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="C30" t="s">
         <v>60</v>
       </c>
       <c r="D30" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="E30" t="s">
         <v>33</v>
       </c>
       <c r="F30" s="5" t="s">
+        <v>155</v>
+      </c>
+      <c r="J30" t="s">
         <v>157</v>
-      </c>
-      <c r="J30" t="s">
-        <v>160</v>
       </c>
     </row>
     <row r="31" spans="1:10" x14ac:dyDescent="0.25">
@@ -2565,7 +2565,7 @@
         <v>1</v>
       </c>
       <c r="B31" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="C31" t="s">
         <v>60</v>
@@ -2577,10 +2577,10 @@
         <v>33</v>
       </c>
       <c r="F31" s="5" t="s">
+        <v>155</v>
+      </c>
+      <c r="J31" t="s">
         <v>157</v>
-      </c>
-      <c r="J31" t="s">
-        <v>160</v>
       </c>
     </row>
     <row r="32" spans="1:10" x14ac:dyDescent="0.25">
@@ -2588,22 +2588,22 @@
         <v>4</v>
       </c>
       <c r="B32" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="C32" t="s">
         <v>61</v>
       </c>
       <c r="D32" t="s">
-        <v>170</v>
+        <v>167</v>
       </c>
       <c r="E32" t="s">
         <v>33</v>
       </c>
       <c r="F32" s="5" t="s">
-        <v>162</v>
+        <v>159</v>
       </c>
       <c r="J32" s="5" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
     </row>
     <row r="33" spans="1:10" x14ac:dyDescent="0.25">
@@ -2611,7 +2611,7 @@
         <v>1</v>
       </c>
       <c r="B33" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="C33" t="s">
         <v>61</v>
@@ -2623,10 +2623,10 @@
         <v>33</v>
       </c>
       <c r="F33" s="5" t="s">
-        <v>163</v>
+        <v>160</v>
       </c>
       <c r="J33" s="5" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
     </row>
     <row r="34" spans="1:10" x14ac:dyDescent="0.25">
@@ -2634,7 +2634,7 @@
         <v>1</v>
       </c>
       <c r="B34" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="C34" t="s">
         <v>60</v>
@@ -2646,10 +2646,10 @@
         <v>33</v>
       </c>
       <c r="F34" s="5" t="s">
-        <v>158</v>
+        <v>171</v>
       </c>
       <c r="J34" t="s">
-        <v>160</v>
+        <v>157</v>
       </c>
     </row>
     <row r="35" spans="1:10" x14ac:dyDescent="0.25">
@@ -2660,19 +2660,19 @@
         <v>1</v>
       </c>
       <c r="B36" t="s">
+        <v>71</v>
+      </c>
+      <c r="C36" t="s">
+        <v>72</v>
+      </c>
+      <c r="E36" t="s">
         <v>73</v>
       </c>
-      <c r="C36" t="s">
+      <c r="F36" s="5" t="s">
         <v>74</v>
       </c>
-      <c r="E36" t="s">
-        <v>75</v>
-      </c>
-      <c r="F36" s="5" t="s">
-        <v>76</v>
-      </c>
       <c r="J36" t="s">
-        <v>160</v>
+        <v>157</v>
       </c>
     </row>
     <row r="37" spans="1:10" x14ac:dyDescent="0.25">
@@ -2680,19 +2680,19 @@
         <v>1</v>
       </c>
       <c r="B37" t="s">
+        <v>75</v>
+      </c>
+      <c r="C37" t="s">
+        <v>76</v>
+      </c>
+      <c r="E37" t="s">
         <v>77</v>
       </c>
-      <c r="C37" t="s">
+      <c r="F37" s="5" t="s">
         <v>78</v>
       </c>
-      <c r="E37" t="s">
-        <v>79</v>
-      </c>
-      <c r="F37" s="5" t="s">
-        <v>80</v>
-      </c>
       <c r="J37" t="s">
-        <v>160</v>
+        <v>157</v>
       </c>
     </row>
     <row r="38" spans="1:10" x14ac:dyDescent="0.25">
@@ -2700,19 +2700,19 @@
         <v>2</v>
       </c>
       <c r="B38" t="s">
+        <v>79</v>
+      </c>
+      <c r="C38" t="s">
+        <v>80</v>
+      </c>
+      <c r="E38" t="s">
         <v>81</v>
       </c>
-      <c r="C38" t="s">
+      <c r="F38" s="5" t="s">
         <v>82</v>
       </c>
-      <c r="E38" t="s">
-        <v>83</v>
-      </c>
-      <c r="F38" s="5" t="s">
-        <v>84</v>
-      </c>
       <c r="J38" t="s">
-        <v>160</v>
+        <v>157</v>
       </c>
     </row>
     <row r="39" spans="1:10" x14ac:dyDescent="0.25">
@@ -2729,13 +2729,13 @@
         <v>67</v>
       </c>
       <c r="E40" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="F40" s="5" t="s">
-        <v>68</v>
+        <v>169</v>
       </c>
       <c r="J40" t="s">
-        <v>160</v>
+        <v>157</v>
       </c>
     </row>
     <row r="41" spans="1:10" x14ac:dyDescent="0.25">
@@ -2743,19 +2743,19 @@
         <v>2</v>
       </c>
       <c r="B41" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="C41" t="s">
         <v>67</v>
       </c>
       <c r="E41" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="F41" s="5" t="s">
-        <v>70</v>
+        <v>170</v>
       </c>
       <c r="J41" t="s">
-        <v>160</v>
+        <v>157</v>
       </c>
     </row>
     <row r="42" spans="1:10" x14ac:dyDescent="0.25">
@@ -2766,16 +2766,16 @@
         <v>66</v>
       </c>
       <c r="C42" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="E42" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="F42" s="5" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="J42" t="s">
-        <v>160</v>
+        <v>157</v>
       </c>
     </row>
     <row r="43" spans="1:10" x14ac:dyDescent="0.25">
@@ -2795,17 +2795,17 @@
         <v>65</v>
       </c>
       <c r="J43" t="s">
-        <v>160</v>
+        <v>157</v>
       </c>
     </row>
     <row r="45" spans="1:10" x14ac:dyDescent="0.25">
       <c r="B45" s="9" t="s">
-        <v>165</v>
+        <v>162</v>
       </c>
     </row>
     <row r="46" spans="1:10" x14ac:dyDescent="0.25">
       <c r="B46" s="7" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
     </row>
     <row r="47" spans="1:10" x14ac:dyDescent="0.25">
@@ -2813,27 +2813,27 @@
     </row>
     <row r="48" spans="1:10" x14ac:dyDescent="0.25">
       <c r="B48" s="6" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
     </row>
     <row r="49" spans="1:15" x14ac:dyDescent="0.25">
       <c r="B49" s="6" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
     </row>
     <row r="50" spans="1:15" x14ac:dyDescent="0.25">
       <c r="B50" s="6" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
     </row>
     <row r="51" spans="1:15" x14ac:dyDescent="0.25">
       <c r="B51" s="6" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
     </row>
     <row r="53" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A53" s="3" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
     </row>
     <row r="54" spans="1:15" x14ac:dyDescent="0.25">
@@ -2841,16 +2841,16 @@
         <v>2</v>
       </c>
       <c r="B54" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="C54" s="5" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="L54" s="3" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="O54" s="5" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
     </row>
   </sheetData>
@@ -2872,37 +2872,37 @@
     <hyperlink ref="F37" r:id="rId15" xr:uid="{00000000-0004-0000-0000-00000F000000}"/>
     <hyperlink ref="F38" r:id="rId16" xr:uid="{00000000-0004-0000-0000-000010000000}"/>
     <hyperlink ref="F15" r:id="rId17" xr:uid="{00000000-0004-0000-0000-000011000000}"/>
-    <hyperlink ref="F40" r:id="rId18" xr:uid="{00000000-0004-0000-0000-000012000000}"/>
-    <hyperlink ref="F41" r:id="rId19" xr:uid="{00000000-0004-0000-0000-000013000000}"/>
-    <hyperlink ref="J32" r:id="rId20" xr:uid="{00000000-0004-0000-0000-000014000000}"/>
-    <hyperlink ref="J33" r:id="rId21" xr:uid="{00000000-0004-0000-0000-000015000000}"/>
-    <hyperlink ref="C54" r:id="rId22" xr:uid="{00000000-0004-0000-0000-000017000000}"/>
-    <hyperlink ref="J6" r:id="rId23" xr:uid="{00000000-0004-0000-0000-000018000000}"/>
-    <hyperlink ref="F20" r:id="rId24" xr:uid="{00000000-0004-0000-0000-000019000000}"/>
-    <hyperlink ref="J7" r:id="rId25" xr:uid="{00000000-0004-0000-0000-00001A000000}"/>
-    <hyperlink ref="F22" r:id="rId26" xr:uid="{00000000-0004-0000-0000-00001B000000}"/>
-    <hyperlink ref="O54" r:id="rId27" xr:uid="{00000000-0004-0000-0000-00001D000000}"/>
-    <hyperlink ref="F24" r:id="rId28" xr:uid="{0DA5FBDE-A9E6-48C7-A3AB-9C6D18E6934A}"/>
-    <hyperlink ref="F16" r:id="rId29" xr:uid="{97709935-7D03-4437-A153-F74893B872B7}"/>
-    <hyperlink ref="F30:F31" r:id="rId30" display="https://www.tme.eu/hr/en/details/zl201-40g/pin-headers/connfly/ds1021-1-40sf11-b/" xr:uid="{6D1EC43E-9D04-417C-B22C-F34EBB95F4FB}"/>
-    <hyperlink ref="J23" r:id="rId31" xr:uid="{B3BEA3C8-45AF-4461-AEBA-B3CF3A651F54}"/>
-    <hyperlink ref="F34" r:id="rId32" xr:uid="{46948A8B-6EC2-4E89-AF34-0564791E4119}"/>
-    <hyperlink ref="F42" r:id="rId33" xr:uid="{FE2FF78F-397D-4B16-A1A0-D8DC2E8DDE30}"/>
-    <hyperlink ref="F3" r:id="rId34" xr:uid="{3393264D-1B1F-4645-B282-8591715A5FD8}"/>
-    <hyperlink ref="F4" r:id="rId35" xr:uid="{77B2F287-2D67-4EDB-B812-9D2E2455569D}"/>
-    <hyperlink ref="F5" r:id="rId36" xr:uid="{A849614D-E4C2-4722-818E-E5575A954759}"/>
-    <hyperlink ref="F6" r:id="rId37" xr:uid="{00BC0B3C-301E-437D-9108-D62EF7BB272D}"/>
-    <hyperlink ref="F7" r:id="rId38" xr:uid="{F954481B-123E-4737-8D9B-9BF253962766}"/>
-    <hyperlink ref="F8" r:id="rId39" xr:uid="{6F2ABE65-0EEB-4829-BE85-EAC7DC43D34C}"/>
-    <hyperlink ref="F9" r:id="rId40" xr:uid="{DB59D5A3-699A-4BDC-B20F-9A0A76A544CE}"/>
-    <hyperlink ref="F10" r:id="rId41" xr:uid="{DE3095A7-8912-439A-B518-2DE646201FA8}"/>
-    <hyperlink ref="F12" r:id="rId42" xr:uid="{72AF700C-C62F-4A68-85E1-015C1DE22969}"/>
-    <hyperlink ref="F30" r:id="rId43" xr:uid="{D27A72D3-14F2-4327-8A7C-99F2AA648DBA}"/>
-    <hyperlink ref="F31" r:id="rId44" xr:uid="{6112AD62-D760-45FA-884B-79BE55E4F128}"/>
-    <hyperlink ref="F23" r:id="rId45" xr:uid="{391EA039-2C02-462F-9643-F020B31CDA02}"/>
-    <hyperlink ref="F32" r:id="rId46" xr:uid="{3E04B101-2D92-41AC-B60D-4692ED670224}"/>
-    <hyperlink ref="F33" r:id="rId47" xr:uid="{0A05E156-C61A-477D-B43C-FE97AEACECF2}"/>
-    <hyperlink ref="J11" r:id="rId48" xr:uid="{C309A78D-41B0-4435-8722-0B1A25E141FE}"/>
+    <hyperlink ref="J32" r:id="rId18" xr:uid="{00000000-0004-0000-0000-000014000000}"/>
+    <hyperlink ref="J33" r:id="rId19" xr:uid="{00000000-0004-0000-0000-000015000000}"/>
+    <hyperlink ref="C54" r:id="rId20" xr:uid="{00000000-0004-0000-0000-000017000000}"/>
+    <hyperlink ref="J6" r:id="rId21" xr:uid="{00000000-0004-0000-0000-000018000000}"/>
+    <hyperlink ref="F20" r:id="rId22" xr:uid="{00000000-0004-0000-0000-000019000000}"/>
+    <hyperlink ref="J7" r:id="rId23" xr:uid="{00000000-0004-0000-0000-00001A000000}"/>
+    <hyperlink ref="F22" r:id="rId24" xr:uid="{00000000-0004-0000-0000-00001B000000}"/>
+    <hyperlink ref="O54" r:id="rId25" xr:uid="{00000000-0004-0000-0000-00001D000000}"/>
+    <hyperlink ref="F24" r:id="rId26" xr:uid="{0DA5FBDE-A9E6-48C7-A3AB-9C6D18E6934A}"/>
+    <hyperlink ref="F16" r:id="rId27" xr:uid="{97709935-7D03-4437-A153-F74893B872B7}"/>
+    <hyperlink ref="F30:F31" r:id="rId28" display="https://www.tme.eu/hr/en/details/zl201-40g/pin-headers/connfly/ds1021-1-40sf11-b/" xr:uid="{6D1EC43E-9D04-417C-B22C-F34EBB95F4FB}"/>
+    <hyperlink ref="J23" r:id="rId29" xr:uid="{B3BEA3C8-45AF-4461-AEBA-B3CF3A651F54}"/>
+    <hyperlink ref="F42" r:id="rId30" xr:uid="{FE2FF78F-397D-4B16-A1A0-D8DC2E8DDE30}"/>
+    <hyperlink ref="F3" r:id="rId31" xr:uid="{3393264D-1B1F-4645-B282-8591715A5FD8}"/>
+    <hyperlink ref="F4" r:id="rId32" xr:uid="{77B2F287-2D67-4EDB-B812-9D2E2455569D}"/>
+    <hyperlink ref="F5" r:id="rId33" xr:uid="{A849614D-E4C2-4722-818E-E5575A954759}"/>
+    <hyperlink ref="F6" r:id="rId34" xr:uid="{00BC0B3C-301E-437D-9108-D62EF7BB272D}"/>
+    <hyperlink ref="F7" r:id="rId35" xr:uid="{F954481B-123E-4737-8D9B-9BF253962766}"/>
+    <hyperlink ref="F8" r:id="rId36" xr:uid="{6F2ABE65-0EEB-4829-BE85-EAC7DC43D34C}"/>
+    <hyperlink ref="F9" r:id="rId37" xr:uid="{DB59D5A3-699A-4BDC-B20F-9A0A76A544CE}"/>
+    <hyperlink ref="F10" r:id="rId38" xr:uid="{DE3095A7-8912-439A-B518-2DE646201FA8}"/>
+    <hyperlink ref="F12" r:id="rId39" xr:uid="{72AF700C-C62F-4A68-85E1-015C1DE22969}"/>
+    <hyperlink ref="F30" r:id="rId40" xr:uid="{D27A72D3-14F2-4327-8A7C-99F2AA648DBA}"/>
+    <hyperlink ref="F31" r:id="rId41" xr:uid="{6112AD62-D760-45FA-884B-79BE55E4F128}"/>
+    <hyperlink ref="F23" r:id="rId42" xr:uid="{391EA039-2C02-462F-9643-F020B31CDA02}"/>
+    <hyperlink ref="F32" r:id="rId43" xr:uid="{3E04B101-2D92-41AC-B60D-4692ED670224}"/>
+    <hyperlink ref="F33" r:id="rId44" xr:uid="{0A05E156-C61A-477D-B43C-FE97AEACECF2}"/>
+    <hyperlink ref="J11" r:id="rId45" xr:uid="{C309A78D-41B0-4435-8722-0B1A25E141FE}"/>
+    <hyperlink ref="F40" r:id="rId46" xr:uid="{32F9AC3E-E5BF-4FC3-A6B1-4D1FC13CE3AD}"/>
+    <hyperlink ref="F41" r:id="rId47" xr:uid="{FC769EF6-2BFE-42A2-93B8-91FA2FFE5ACE}"/>
+    <hyperlink ref="F34" r:id="rId48" xr:uid="{C94DD01E-0E07-4D9E-BEB3-FAD4FFB9765F}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId49"/>
